--- a/data/prom/stock-template.xlsx
+++ b/data/prom/stock-template.xlsx
@@ -702,61 +702,56 @@
           <t>Значення_Характеристики</t>
         </is>
       </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Назва_Характеристики</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Одиниця_виміру_Характеристики</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Значення_Характеристики</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4633719219208</t>
+          <t>8316507127494</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Мягкая игрушка подушка Куроми Kuromi Sanrio 50×50 см плюшевая декоративная подушка подарок</t>
+          <t>Кулон «Демон с цепочкой»</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>М'яка іграшка подушка Куромі Kuromi Sanrio 50×50 см плюшева декоративна подушка подарунок</t>
+          <t>Кулон «Демон з ціпком» на ланцюжку</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>куроми, kuromi, sanrio, мягкая игрушка куроми, подушка куроми, плюшевая куроми, kuromi plush, kuromi pillow, игрушка sanrio, аниме подушка, декоративная подушка, мягкая подушка, подарок аниме, кавай игрушка, подушка 50х50</t>
+          <t>кулон демон, подвеска демон, кулон с крыльями, кулон на цепочке, металлический кулон, готическое украшение, gothic jewelry, demon necklace, альтернативная мода, аксессуар в стиле готика, серебристый кулон, подарок</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>куромі, kuromi, sanrio, м'яка іграшка куромі, подушка куромі, плюшева куромі, kuromi plush, kuromi pillow, іграшка sanrio, аніме подушка, декоративна подушка, м'яка подушка, подарунок аніме, кавай іграшка, подушка 50х50</t>
+          <t>кулон демон, підвіска демон, кулон з крилами, кулон на ланцюжку, металевий кулон, готична прикраса, gothic jewelry, demon necklace, альтернативна мода, аксесуар у стилі готика, сріблястий кулон, подарунок</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>&lt;p data-end="1133" data-start="911"&gt;Большая мягкая подушка &lt;strong data-end="953" data-start="934"&gt;Куроми (Kuromi)&lt;/strong&gt; станет отличным подарком для поклонников персонажей &lt;strong data-end="1016" data-start="1006"&gt;Sanrio&lt;/strong&gt;. Благодаря пушистому плюшу и большому размеру она идеально подходит для сна, отдыха, украшения комнаты и фотосессий.&lt;/p&gt;
-&lt;p data-end="1265" data-start="1135"&gt;Подушка очень приятная на ощупь, хорошо держит форму и станет ярким элементом интерьера или любимой игрушкой для детей и взрослых.&lt;/p&gt;
-&lt;h3 data-end="1286" data-section-id="pf9b3p" data-start="1267"&gt;Характеристики:&lt;/h3&gt;
-&lt;ul data-end="1446" data-start="1287"&gt;
-&lt;li data-end="1309" data-section-id="7pph5n" data-start="1287"&gt;Персонаж: &lt;strong data-end="1309" data-start="1299"&gt;Kuromi&lt;/strong&gt;&lt;/li&gt;
-&lt;li data-end="1329" data-section-id="1g6e2ft" data-start="1310"&gt;Серия: &lt;strong data-end="1329" data-start="1319"&gt;Sanrio&lt;/strong&gt;&lt;/li&gt;
-&lt;li data-end="1352" data-section-id="jcjl9y" data-start="1330"&gt;Размер: &lt;strong data-end="1352" data-start="1340"&gt;50&amp;times;50 см&lt;/strong&gt;&lt;/li&gt;
-&lt;li data-end="1376" data-section-id="1t4h0pv" data-start="1353"&gt;Материал: мягкий плюш&lt;/li&gt;
-&lt;li data-end="1446" data-section-id="1taivyq" data-start="1416"&gt;Цвет: чёрный, белый, розовый&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p data-end="1517" data-start="1448"&gt;Отличный подарок на день рождения, Новый год и любой другой праздник.&lt;/p&gt;</t>
+          <t>Металлический кулон в виде демона с крыльями и хвостом на цепочке. Подвеска выполнена в серебристом цвете с детализированным дизайном. Отлично подойдёт в качестве стильного аксессуара для повседневного образа, тематических мероприятий или подарка.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>&lt;p data-end="485" data-start="261"&gt;Велика м&amp;#39;яка подушка &lt;strong data-end="301" data-start="282"&gt;Куромі (Kuromi)&lt;/strong&gt; стане чудовим подарунком для шанувальників персонажів &lt;strong data-end="366" data-start="356"&gt;Sanrio&lt;/strong&gt;. Завдяки пухнастому плюшу та великому розміру вона чудово підходить для сну, відпочинку, декору кімнати або фотосесій.&lt;/p&gt;
-&lt;p data-end="619" data-start="487"&gt;Подушка дуже приємна на дотик, добре тримає форму та стане яскравою прикрасою інтер&amp;#39;єру або улюбленою іграшкою для дітей і дорослих.&lt;/p&gt;
-&lt;h3 data-end="640" data-section-id="pf9b3p" data-start="621"&gt;Характеристики:&lt;/h3&gt;
-&lt;ul data-end="798" data-start="641"&gt;
-&lt;li data-end="663" data-section-id="7pph5n" data-start="641"&gt;Персонаж: &lt;strong data-end="663" data-start="653"&gt;Kuromi&lt;/strong&gt;&lt;/li&gt;
-&lt;li data-end="683" data-section-id="1cbx7xz" data-start="664"&gt;Серія: &lt;strong data-end="683" data-start="673"&gt;Sanrio&lt;/strong&gt;&lt;/li&gt;
-&lt;li data-end="706" data-section-id="sskcjf" data-start="684"&gt;Розмір: &lt;strong data-end="706" data-start="694"&gt;50&amp;times;50 см&lt;/strong&gt;&lt;/li&gt;
-&lt;li data-end="730" data-section-id="1967hsp" data-start="707"&gt;Матеріал: м&amp;#39;який плюш&lt;/li&gt;
-&lt;li data-end="798" data-section-id="d74k25" data-start="767"&gt;Колір: чорний, білий, рожевий&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p data-end="886" data-start="800"&gt;Ідеально підходить як подарунок на день народження, Новий рік або будь-яке інше свято.&lt;/p&gt;</t>
+          <t>Металевий кулон у вигляді демона з крилами та хвостом на ланцюжку. Підвіска виконана у сріблястому кольорі з деталізованим дизайном. Чудово підійде як стильний аксесуар для повсякденного образу, тематичних заходів або як подарунок.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -766,7 +761,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,7 +778,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7477608519_myagkaya-igrushka-podushka.jpg</t>
+          <t>https://images.prom.ua/7512520982_kulon-demon-s.jpg</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -792,27 +787,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://prom.ua/Myagkie-plyushevye-igrushki</t>
+          <t>https://prom.ua/Kulony</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>3088231882</v>
+        <v>3104580551</v>
       </c>
       <c r="AA2" t="n">
-        <v>2604</v>
+        <v>15090303</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -821,7 +816,7 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3088231882-myagkaya-igrushka-podushka.html</t>
+          <t>https://cs4101246.prom.ua/p3104580551-kulon-demon-tsepochkoj.html</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr"/>
@@ -848,79 +843,50 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Матеріал</t>
+          <t>Вид виробу</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>Плюш</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>Стан</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>Новий</t>
+          <t>Кулон</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1998543502408</t>
+          <t>5332804116779</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Мягкая игрушка Свинка с клубникой плюшевая подушка кавай розовый поросёнок подарок</t>
+          <t>Чёрный чокер с крестиком</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>М'яка іграшка Свинка з полуницею плюшева подушка кавай рожеве поросятко подарунок</t>
+          <t>Чорний чокер з хрестиком</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>мягкая игрушка свинка, плюшевая свинка, свинка с клубникой, кавай свинка, плюшевая подушка свинка, розовая свинка, милая игрушка, kawaii pig, pig plush, плюшевая игрушка, подушка свинка, подарок ребёнку, подарок девушке, декоративная подушка, мягкая подушка</t>
+          <t>чокер, чёрный чокер, чокер с крестиком, чокер из искусственной кожи, gothic choker, gothic jewelry, готический чокер, альтернативная мода, панк аксессуары, рок аксессуары, женский чокер, аксессуар на шею</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>м'яка іграшка свинка, плюшева свинка, свинка з полуницею, кавай свинка, плюшева подушка свинка, рожева свинка, мила іграшка, kawaii pig, pig plush, плюшева іграшка, подушка свинка, подарунок дитині, подарунок дівчині, декоративна подушка, м'яка подушка</t>
+          <t>чокер, чорний чокер, чокер з хрестиком, чокер зі штучної шкіри, gothic choker, gothic jewelry, готичний чокер, альтернативна мода, панк аксесуари, рок аксесуари, жіночий чокер, аксесуар на шию</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>&lt;p data-end="1100" data-start="882"&gt;Милая плюшевая &lt;strong data-end="919" data-start="897"&gt;свинка с клубникой&lt;/strong&gt; станет прекрасным подарком для детей и взрослых. Благодаря нежному материалу и забавному дизайну игрушка отлично подходит для сна, отдыха, украшения комнаты или коллекционирования.&lt;/p&gt;
-&lt;p data-end="1238" data-start="1102"&gt;Мягкий плюш и качественный наполнитель обеспечивают комфорт, а оригинальная клубничка на голове делает игрушку ещё более очаровательной.&lt;/p&gt;
-&lt;p data-end="1256" data-start="1240"&gt;&lt;strong data-end="1256" data-start="1240"&gt;Особенности:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul data-end="1468" data-start="1257"&gt;
-&lt;li data-end="1291" data-section-id="1l5p38b" data-start="1257"&gt;Очень мягкий и приятный материал&lt;/li&gt;
-&lt;li data-end="1328" data-section-id="5my4qs" data-start="1292"&gt;Оригинальный дизайн в стиле kawaii&lt;/li&gt;
-&lt;li data-end="1372" data-section-id="s3xas4" data-start="1329"&gt;Можно использовать как подушку для отдыха&lt;/li&gt;
-&lt;li data-end="1432" data-section-id="1x1p02o" data-start="1373"&gt;Отличный подарок детям и любителям милых плюшевых игрушек&lt;/li&gt;
-&lt;li data-end="1468" data-section-id="1go4v4n" data-start="1433"&gt;Красиво дополнит интерьер комнаты&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Стильный чёрный чокер с декоративной подвеской в виде крестика. Изготовлен из искусственной кожи, имеет регулируемую застёжку для комфортной посадки. Отлично дополнит готические, альтернативные, рок, панк и повседневные образы.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>&lt;p data-end="457" data-start="245"&gt;Мила плюшева &lt;strong data-end="280" data-start="258"&gt;свинка з полуницею&lt;/strong&gt; стане чудовим подарунком для дітей та дорослих. Завдяки ніжному матеріалу та кумедному дизайну іграшка чудово підходить для сну, відпочинку, декору кімнати або колекціонування.&lt;/p&gt;
-&lt;p data-end="616" data-start="459"&gt;Приємний на дотик плюш і м&amp;#39;який наповнювач забезпечують максимальний комфорт, а оригінальний дизайн із полуничкою на голові робить іграшку ще більш чарівною.&lt;/p&gt;
-&lt;p data-end="634" data-start="618"&gt;&lt;strong data-end="634" data-start="618"&gt;Особливості:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul data-end="857" data-start="635"&gt;
-&lt;li data-end="669" data-section-id="pma0yc" data-start="635"&gt;Дуже м&amp;#39;який та приємний матеріал&lt;/li&gt;
-&lt;li data-end="706" data-section-id="9v43e3" data-start="670"&gt;Оригінальний дизайн у стилі kawaii&lt;/li&gt;
-&lt;li data-end="744" data-section-id="uudtt3" data-start="707"&gt;Підходить як подушка для відпочинку&lt;/li&gt;
-&lt;li data-end="814" data-section-id="d85jz" data-start="745"&gt;Чудовий подарунок для дітей та шанувальників милих плюшевих іграшок&lt;/li&gt;
-&lt;li data-end="857" data-section-id="rehel9" data-start="815"&gt;Гарно доповнить інтер&amp;#39;єр дитячої кімнати&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Стильний чорний чокер із декоративною підвіскою у вигляді хрестика. Виготовлений зі штучної шкіри, має регульовану застібку для комфортної посадки. Чудово доповнить готичні, альтернативні, рок, панк та повсякденні образи.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -930,7 +896,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>425</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -947,36 +913,36 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7477616205_myagkaya-igrushka-svinka.jpg</t>
+          <t>https://images.prom.ua/7512527741_chyornyj-choker-s.jpg</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://prom.ua/Myagkie-plyushevye-igrushki</t>
+          <t>https://prom.ua/Kulony</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>3088233582</v>
+        <v>3104590826</v>
       </c>
       <c r="AA3" t="n">
-        <v>2604</v>
+        <v>15090303</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -985,7 +951,7 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3088233582-myagkaya-igrushka-svinka.html</t>
+          <t>https://cs4101246.prom.ua/p3104590826-chyornyj-choker-krestikom.html</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr"/>
@@ -999,26 +965,6 @@
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Одеса</t>
@@ -1026,101 +972,56 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Товару немає в наявності</t>
-        </is>
-      </c>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Колір</t>
+          <t>Матеріал</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>Рожевий</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>Матеріал</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>Плюш</t>
+          <t>Штучна шкіра</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5748011423663</t>
+          <t>5268473096074</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Оригинальная фигурка Vocaloid FurYu Hatsune Miku Kagamine Rin Kagamine Len коллекционная аниме фигурка</t>
+          <t>Кулон-граната Джинкс — Arcane / League of Legends</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Оригінальна фігурка Vocaloid FurYu Hatsune Miku Kagamine Rin Kagamine Len колекційна аніме фігурка</t>
+          <t>Кулон-граната Джінкс — Arcane / League of Legends</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>vocaloid, furyu, фигурка vocaloid, hatsune miku, kagamine rin, kagamine len, оригинальная фигурка, аниме фигурка, коллекционная фигурка, miku figure, furyu figure, vocaloid figure, фигурка хатсуне мику, подарок аниме, фигурка манга</t>
+          <t>кулон джинкс, граната джинкс, arcane, league of legends, lol, jinx, jinx grenade, jinx necklace, кулон arcane, кулон league of legends, подвеска джинкс, мерч arcane, мерч league of legends, косплей джинкс</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>vocaloid, furyu, фігурка vocaloid, hatsune miku, kagamine rin, kagamine len, оригінальна фігурка, аніме фігурка, колекційна фігурка, miku figure, furyu figure, vocaloid figure, фігурка хатсуне міку, подарунок аніме, фігурка манга</t>
+          <t>кулон джінкс, граната джінкс, arcane, league of legends, lol, jinx, jinx grenade, jinx necklace, кулон arcane, кулон league of legends, підвіска джінкс, мерч arcane, мерч league of legends, косплей джінкс</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>&lt;p data-end="1206" data-start="933"&gt;Оригинальная коллекционная фигурка &lt;strong data-end="980" data-start="968"&gt;Vocaloid&lt;/strong&gt; от &lt;strong data-end="993" data-start="984"&gt;Furyu&lt;/strong&gt; с очаровательным дизайном, где персонажи сидят под маленьким зонтиком внутри декоративной круглой подставки. Минималистичный стиль и качественное исполнение делают её прекрасным дополнением любой аниме-коллекции.&lt;/p&gt;
-&lt;p data-end="1250" data-start="1208"&gt;В серии представлены популярные персонажи:&lt;/p&gt;
-&lt;ul data-end="1295" data-start="1251"&gt;
-&lt;li data-end="1265" data-section-id="1vbgy8y" data-start="1251"&gt;Hatsune Miku&lt;/li&gt;
-&lt;li data-end="1280" data-section-id="d4dkce" data-start="1266"&gt;Kagamine Rin&lt;/li&gt;
-&lt;li data-end="1295" data-section-id="d4d224" data-start="1281"&gt;Kagamine Len&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p data-end="1410" data-start="1297"&gt;Фигурка станет отличным подарком для поклонников Vocaloid, украсит рабочий стол, полку или витрину коллекционера.&lt;/p&gt;
-&lt;p data-end="1428" data-start="1412"&gt;&lt;strong data-end="1428" data-start="1412"&gt;Особенности:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul data-end="1581" data-start="1429"&gt;
-&lt;li data-end="1459" data-section-id="ngfbkd" data-start="1429"&gt;Оригинальная продукция Furyu&lt;/li&gt;
-&lt;li data-end="1481" data-section-id="8gyawd" data-start="1460"&gt;Высокая детализация&lt;/li&gt;
-&lt;li data-end="1504" data-section-id="oo29eb" data-start="1482"&gt;Качественный пластик&lt;/li&gt;
-&lt;li data-end="1538" data-section-id="gq6ton" data-start="1505"&gt;Стильная декоративная подставка&lt;/li&gt;
-&lt;li data-end="1581" data-section-id="1sg8g09" data-start="1539"&gt;Отлично подходит для коллекции и подарка&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Металлический кулон в виде гранаты Джинкс из сериала &lt;strong data-end="760" data-start="750"&gt;Arcane&lt;/strong&gt; и вселенной &lt;strong data-end="794" data-start="773"&gt;League of Legends&lt;/strong&gt;. Подвеска выполнена с высокой детализацией и дополнена металлической цепочкой. Отлично подойдёт для косплея, тематических мероприятий, фотосессий или в качестве подарка поклонникам Arcane и League of Legends.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&lt;p data-end="539" data-start="282"&gt;Оригінальна колекційна фігурка &lt;strong data-end="325" data-start="313"&gt;Vocaloid&lt;/strong&gt; від &lt;strong data-end="339" data-start="330"&gt;Furyu&lt;/strong&gt; із чарівним дизайном, де персонажі сидять під маленькою парасолькою в декоративній круглій підставці. Мінімалістичний стиль і якісне виконання роблять її чудовим доповненням будь-якої аніме-колекції.&lt;/p&gt;
-&lt;p data-end="582" data-start="541"&gt;У серії представлені популярні персонажі:&lt;/p&gt;
-&lt;ul data-end="627" data-start="583"&gt;
-&lt;li data-end="597" data-section-id="1vbgy8y" data-start="583"&gt;Hatsune Miku&lt;/li&gt;
-&lt;li data-end="612" data-section-id="d4dkce" data-start="598"&gt;Kagamine Rin&lt;/li&gt;
-&lt;li data-end="627" data-section-id="d4d224" data-start="613"&gt;Kagamine Len&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p data-end="747" data-start="629"&gt;Фігурка стане чудовим подарунком для шанувальників Vocaloid, прикрасить робочий стіл, полицю або вітрину колекціонера.&lt;/p&gt;
-&lt;p data-end="765" data-start="749"&gt;&lt;strong data-end="765" data-start="749"&gt;Особливості:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul data-end="908" data-start="766"&gt;
-&lt;li data-end="795" data-section-id="1607y4i" data-start="766"&gt;Оригінальна продукція Furyu&lt;/li&gt;
-&lt;li data-end="820" data-section-id="yhplrt" data-start="796"&gt;Деталізоване виконання&lt;/li&gt;
-&lt;li data-end="838" data-section-id="1k2gnc3" data-start="821"&gt;Якісний пластик&lt;/li&gt;
-&lt;li data-end="870" data-section-id="62cn2n" data-start="839"&gt;Стильна декоративна підставка&lt;/li&gt;
-&lt;li data-end="908" data-section-id="18xgck2" data-start="871"&gt;Ідеально для колекції або подарунка&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Металевий кулон у вигляді гранати Джінкс із серіалу &lt;strong data-end="142" data-start="132"&gt;Arcane&lt;/strong&gt; та всесвіту &lt;strong data-end="176" data-start="155"&gt;League of Legends&lt;/strong&gt;. Підвіска виконана з високою деталізацією та доповнена металевим ланцюжком. Чудово підійде для косплею, тематичних заходів, фотосесій або як подарунок для шанувальників Arcane та League of Legends.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1130,7 +1031,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>550</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1147,45 +1048,45 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7477646229_originalnaya-figurka-vocaloid.jpg</t>
+          <t>https://images.prom.ua/7512538938_kulon-granata-dzhinks-.jpg</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://prom.ua/Detskie-igrovye-figurki</t>
+          <t>https://prom.ua/Kulony</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>3088238932</v>
+        <v>3104601784</v>
       </c>
       <c r="AA4" t="n">
-        <v>2638</v>
+        <v>15090303</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="n">
-        <v>977038778</v>
-      </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3088238932-originalnaya-figurka-vocaloid.html</t>
+          <t>https://cs4101246.prom.ua/p3104601784-kulon-granata-dzhinks.html</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
@@ -1206,53 +1107,47 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Товару немає в наявності</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>Персонаж</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>Hatsune Miku</t>
-        </is>
-      </c>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2734491553978</t>
+          <t>8975604601251</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Оригинальная фигурка Vocaloid FurYu Hatsune Miku Kagamine Rin Kagamine Len коллекционная аниме фигурка</t>
+          <t>Кулон «Сердце с крылышками» на цепочке</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Оригінальна фігурка Vocaloid FurYu Hatsune Miku Kagamine Rin Kagamine Len колекційна аніме фігурка Kagamine Rin</t>
+          <t>Кулон «Серце з крильцями» на ланцюжку</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>vocaloid, furyu, фигурка vocaloid, hatsune miku, kagamine rin, kagamine len, оригинальная фигурка, аниме фигурка, коллекционная фигурка, miku figure, furyu figure, vocaloid figure, фигурка хатсуне мику, подарок аниме, фигурка манга</t>
+          <t>кулон сердце, кулон с крылышками, подвеска сердце, кулон летучая мышь, готическое украшение, gothic jewelry, heart necklace, bat wings necklace, kawaii аксессуары, альтернативная мода, металлический кулон, подарок</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>vocaloid, furyu, фігурка vocaloid, hatsune miku, kagamine rin, kagamine len, оригінальна фігурка, аніме фігурка, колекційна фігурка, miku figure, furyu figure, vocaloid figure, фігурка хатсуне міку, подарунок аніме, фігурка манга</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>кулон серце, кулон з крильцями, підвіска серце, кулон кажан, готична прикраса, gothic jewelry, heart necklace, bat wings necklace, kawaii аксесуари, альтернативна мода, металевий кулон, подарунок</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Металлический кулон в виде розового сердца с декоративными крыльями летучей мыши на цепочке. Подвеска выполнена с яркими цветными элементами и детализированным дизайном. Отлично подойдёт в качестве стильного аксессуара для повседневных, готических, альтернативных или kawaii-образов, а также в качестве подарка.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Металевий кулон у вигляді рожевого серця з декоративними крильцями кажана на ланцюжку. Підвіска виконана з яскравими кольоровими елементами та деталізованим дизайном. Чудово підійде як стильний аксесуар для повсякденних, готичних, альтернативних або kawaii-образів, а також як подарунок.</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>r</t>
@@ -1260,7 +1155,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>425</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1277,45 +1172,45 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7477646886_originalnaya-figurka-vocaloid.jpg</t>
+          <t>https://images.prom.ua/7512547856_kulon-serdtse-s.jpg</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://prom.ua/Detskie-igrovye-figurki</t>
+          <t>https://prom.ua/Kulony</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>3088239578</v>
+        <v>3104611061</v>
       </c>
       <c r="AA5" t="n">
-        <v>2638</v>
+        <v>15090303</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="n">
-        <v>977038778</v>
-      </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3088239578-originalnaya-figurka-vocaloid.html</t>
+          <t>https://cs4101246.prom.ua/p3104611061-kulon-serdtse-krylyshkami.html</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr"/>
@@ -1336,53 +1231,47 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Товару немає в наявності</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>Персонаж</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>Kagamine Rin</t>
-        </is>
-      </c>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4221699751008</t>
+          <t>0857462843671</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Оригинальная фигурка Vocaloid FurYu Hatsune Miku Kagamine Rin Kagamine Len коллекционная аниме фигурка</t>
+          <t>Чёрный берет-кепка в стиле Punk / Gothic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Оригінальна фігурка Vocaloid FurYu Hatsune Miku Kagamine Rin Kagamine Len колекційна аніме фігурка Kagamine Len</t>
+          <t>Чорний берет-кепка у стилі Punk / Gothic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>vocaloid, furyu, фигурка vocaloid, hatsune miku, kagamine rin, kagamine len, оригинальная фигурка, аниме фигурка, коллекционная фигурка, miku figure, furyu figure, vocaloid figure, фигурка хатсуне мику, подарок аниме, фигурка манга</t>
+          <t>берет кепка, чёрный берет, чёрная кепка, punk fashion, gothic fashion, grunge style, harajuku, альтернативная мода, кепка с цепочками, берет с козырьком, emo style, японская мода</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>vocaloid, furyu, фігурка vocaloid, hatsune miku, kagamine rin, kagamine len, оригінальна фігурка, аніме фігурка, колекційна фігурка, miku figure, furyu figure, vocaloid figure, фігурка хатсуне міку, подарунок аніме, фігурка манга</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>берет кепка, чорний берет, чорна кепка, punk fashion, gothic fashion, grunge style, harajuku, альтернативна мода, кепка з ланцюжками, берет з козирком, emo style, японська мода</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Стильный чёрный берет-кепка с жёстким козырьком, декоративными цепочками, английскими булавками и клетчатой вставкой. Модель выполнена в альтернативном стиле и отлично дополнит готические, панк, grunge, emo, Harajuku и повседневные образы.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Стильний чорний берет-кепка з жорстким козирком, декоративними ланцюжками, англійськими шпильками та картатою вставкою. Модель виконана в альтернативному стилі та чудово доповнить готичні, панк, grunge, emo, Harajuku та повсякденні образи.</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>r</t>
@@ -1390,7 +1279,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1407,45 +1296,45 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7477647307_originalnaya-figurka-vocaloid.jpg</t>
+          <t>https://images.prom.ua/7512562173_chyornyj-beret-kepka-v.jpg</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://prom.ua/Detskie-igrovye-figurki</t>
+          <t>https://prom.ua/Golovnye-ubory-zhenskie-obschee</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>3088239579</v>
+        <v>3104620881</v>
       </c>
       <c r="AA6" t="n">
-        <v>2638</v>
+        <v>32716</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="n">
-        <v>977038778</v>
-      </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3088239579-originalnaya-figurka-vocaloid.html</t>
+          <t>https://cs4101246.prom.ua/p3104620881-chyornyj-beret-kepka.html</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr"/>
@@ -1459,6 +1348,26 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Одеса</t>
@@ -1466,60 +1375,47 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Товару немає в наявності</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>Персонаж</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>Kagamine Len</t>
-        </is>
-      </c>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4527006316957</t>
+          <t>1568472039029</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Мягкая игрушка Pusheen 16х16 см</t>
+          <t>Чёрная готическая корона с камнями</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>М'яка іграшка Pusheen 16х16 см</t>
+          <t>Чорна готична корона з камінцями</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pusheen, игрушка pusheen, мягкая игрушка pusheen, плюшевый котик, плюшевая игрушка, котик pusheen, мягкий котик, подарок для девушки, декоративная игрушка, плюшевая подушка, kawaii, аниме мерч</t>
+          <t>чёрная корона, корона с камнями, готическая корона, корона готика, чёрная тиара, тиара с камнями, корона для косплея, корона на парик, корона тёмной королевы, готические аксессуары, gothic crown, black crown, black tiara, cosplay crown, dark queen, gothic accessories, lolita</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>pusheen, іграшка pusheen, м'яка іграшка pusheen, плюшевий котик, плюшева іграшка, котик pusheen, м'який котик, подарунок для дівчини, декоративна іграшка, плюшева подушка, kawaii, аніме мерч</t>
+          <t>чорна корона, корона з камінцями, готична корона, корона готика, чорна тіара, тіара з камінням, корона для косплею, корона на перуку, корона темної королеви, готичні аксесуари, gothic crown, black crown, black tiara, cosplay crown, dark queen, gothic accessories, lolita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Мягкая игрушка Pusheen в виде милого котика в тёплом зимнем образе. Игрушка выполнена из приятного на ощупь плюшевого материала и имеет компактный размер 16х16 см. Подойдёт в качестве подарка, украшения комнаты или дополнения к коллекции поклонников Pusheen.</t>
+          <t>&lt;p data-end="1044" data-start="830"&gt;Эффектная чёрная корона в готическом стиле, украшенная крупными и мелкими чёрными камнями. Ажурный металлический дизайн, декоративные элементы и высокие пики создают выразительный королевский образ.&lt;/p&gt;
+&lt;p data-end="1206" data-start="1046"&gt;Корона хорошо держит форму и отлично смотрится на парике. Подойдёт для &lt;strong data-end="1205" data-start="1117"&gt;готических образов, косплея, фотосессий, Halloween, Lolita и образов тёмной королевы&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>М&amp;#39;яка іграшка Pusheen у вигляді милого котика в теплому зимовому образі. Іграшка виконана з приємного на дотик плюшевого матеріалу та має компактний розмір 16х16 см. Підійде як подарунок, прикраса кімнати або доповнення до колекції шанувальників Pusheen.</t>
+          <t>&lt;p data-end="268" data-start="65"&gt;Ефектна чорна корона в готичному стилі, прикрашена великими та дрібними чорними камінцями. Ажурний металевий дизайн, декоративні елементи та високі піки створюють виразний королівський образ.&lt;/p&gt;
+&lt;p data-end="425" data-start="270"&gt;Корона добре тримає форму та чудово виглядає на перуці. Підійде для &lt;strong data-end="424" data-start="338"&gt;готичних образів, косплею, фотосесій, Halloween, Lolita та образів темної королеви&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1529,7 +1425,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1546,36 +1442,36 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7502814610_myagkaya-igrushka-pusheen.jpg</t>
+          <t>https://images.prom.ua/7659906350_chyornaya-goticheskaya-korona.jpg, https://images.prom.ua/7659906339_chyornaya-goticheskaya-korona.jpg</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://prom.ua/Myagkie-plyushevye-igrushki</t>
+          <t>https://prom.ua/Karnavalnye-aksessuary</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>3099415903</v>
+        <v>3171899914</v>
       </c>
       <c r="AA7" t="n">
-        <v>2604</v>
+        <v>34706</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1584,7 +1480,7 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3099415903-myagkaya-igrushka-pusheen.html</t>
+          <t>https://cs4101246.prom.ua/p3171899914-chyornaya-goticheskaya-korona.html</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr"/>
@@ -1605,51 +1501,58 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Товару немає в наявності</t>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>Колір</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Чорний</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0195169878622</t>
+          <t>7982145611101</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Мягкая игрушка Pusheen S’mores — 18 см</t>
+          <t>Чёрные колготки в сетку с принтом паутины</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>М’яка іграшка Pusheen S’mores — 18 см</t>
+          <t>Чорні колготки в сіточку з принтом павутиння</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pusheen, Пушин, Пушин кот, игрушка Pusheen, мягкая игрушка, плюшевая игрушка, Pusheen S’mores, S’more, смор, кот Пушин, игрушка кот, kawaii, кавай, плюшевый кот, игрушка 18 см, Pusheen plush</t>
+          <t>колготки в сетку, чёрные колготки, колготки паутина, колготки с паутиной, ажурные колготки, готические колготки, колготки для косплея, чёрная сетка, готическая одежда, альтернативный стиль, fishnet tights, spider web tights, gothic tights, black fishnet, goth stockings, punk tights, Halloween tights</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pusheen, Пушин, Пушін, іграшка Pusheen, м’яка іграшка, плюшева іграшка, Pusheen S’mores, S’more, смор, кіт Пушин, іграшка кіт, kawaii, кавай, плюшевий кіт, іграшка 18 см, Pusheen plush</t>
+          <t>колготки в сіточку, чорні колготки, колготки павутиння, колготки з павутиною, ажурні колготки, готичні колготки, колготки для косплею, чорна сіточка, готичний одяг, альтернативний стиль, fishnet tights, spider web tights, gothic tights, black fishnet, goth stockings, punk tights, Halloween tights</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>&lt;p data-end="891" data-start="710"&gt;Милая мягкая игрушка &lt;strong data-end="758" data-start="747"&gt;Pusheen&lt;/strong&gt; в виде сладкого &lt;strong data-end="793" data-start="775"&gt;смора (S&amp;rsquo;more)&lt;/strong&gt;. Пушин расположилась между двумя крекерами и шоколадом, превратившись в забавный плюшевый десерт.&lt;/p&gt;
-&lt;p data-end="1036" data-start="893"&gt;Компактный размер &lt;strong data-end="920" data-start="911"&gt;18 см&lt;/strong&gt; делает игрушку отличным украшением комнаты, коллекции или милым подарком для поклонников Pusheen и kawaii-эстетики.&lt;/p&gt;</t>
+          <t>&lt;p data-end="974" data-start="814"&gt;Эффектные чёрные колготки в сетку с узором в виде паутины. Сочетание мелкой сетки и крупного готического принта делает их ярким акцентом образа.&lt;/p&gt;
+&lt;p data-end="1101" data-start="976"&gt;Отлично дополнят &lt;strong data-end="1057" data-start="993"&gt;готический, альтернативный, punk, grunge или Halloween образ&lt;/strong&gt;, а также подойдут для косплея и фотосессий.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;p data-end="251" data-start="70"&gt;Мила м&amp;rsquo;яка іграшка &lt;strong data-end="112" data-start="101"&gt;Pusheen&lt;/strong&gt; у вигляді солодкого &lt;strong data-end="151" data-start="133"&gt;смору (S&amp;rsquo;more)&lt;/strong&gt;. Пушин розташувалася між двома крекерами та шоколадом, перетворившись на кумедний пухнастий десерт.&lt;/p&gt;
-&lt;p data-end="398" data-start="253"&gt;Компактний розмір &lt;strong data-end="280" data-start="271"&gt;18 см&lt;/strong&gt; робить іграшку чудовою прикрасою кімнати, колекції або милим подарунком для шанувальників Pusheen та kawaii-естетики.&lt;/p&gt;</t>
+          <t>&lt;p data-end="244" data-start="77"&gt;Ефектні чорні колготки в сіточку з візерунком у вигляді павутиння. Поєднання дрібної сітки та великого готичного принта робить їх яскравим акцентом образу.&lt;/p&gt;
+&lt;p data-end="370" data-start="246"&gt;Чудово доповнять &lt;strong data-end="325" data-start="263"&gt;готичний, альтернативний, punk, grunge або Halloween образ&lt;/strong&gt;, а також підійдуть для косплею та фотосесій.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1659,7 +1562,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1676,7 +1579,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7644832559_myagkaya-igrushka-pusheen.jpg</t>
+          <t>https://images.prom.ua/7659930849_chyornye-kolgotki-v.jpg</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1685,27 +1588,27 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://prom.ua/Myagkie-plyushevye-igrushki</t>
+          <t>https://prom.ua/Kolgoty-i-chulki-zhenskie</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>3163897183</v>
+        <v>3171906156</v>
       </c>
       <c r="AA8" t="n">
-        <v>2604</v>
+        <v>304</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1617,7 @@
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3163897183-myagkaya-igrushka-pusheen.html</t>
+          <t>https://cs4101246.prom.ua/p3171906156-chyornye-kolgotki-setku.html</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr"/>
@@ -1739,43 +1642,76 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>Колір</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Чорний</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Вид виробу</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>Колготки</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>Сітка</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9453214827076</t>
+          <t>6591043348502</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Тетрадь Death Note — Тетрадь смерти</t>
+          <t>Капроновые колготки с пауками и паутиной</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Зошит Death Note — Зошит смерті</t>
+          <t>Капронові колготки з павуками та павутинням</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>тетрадь смерти, тетрадь Death Note, блокнот Death Note, Дез Нот, Лайт Ягами, Ягами Лайт, Кира, Рюк, аниме тетрадь, аниме блокнот, аниме мерч, тетрадь Киры, Death Note notebook, Light Yagami, Kira, Ryuk, anime notebook, Death Note merch</t>
+          <t>капроновые колготки, колготки с пауками, колготки с паутиной, чёрные колготки, прозрачные колготки, готические колготки, колготки Halloween, колготки для косплея, паук, паутина, готический стиль, альтернативная одежда, spider tights, spider web tights, gothic tights, sheer tights, Halloween tights, goth stockings</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>зошит смерті, зошит Death Note, блокнот Death Note, Дез Нот, Лайт Яґамі, Яґамі Лайт, Кіра, Рюк, аніме зошит, аніме блокнот, аніме мерч, зошит Кіри, Death Note notebook, Light Yagami, Kira, Ryuk, anime notebook, Death Note merch</t>
+          <t>капронові колготки, колготки з павуками, колготки з павутинням, чорні колготки, прозорі колготки, готичні колготки, колготки Halloween, колготки для косплею, павук, павутина, готичний стиль, альтернативний одяг, spider tights, spider web tights, gothic tights, sheer tights, Halloween tights, goth stockings</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Чёрная тетрадь, выполненная в стиле легендарного &lt;strong data-end="887" data-start="873"&gt;Death Note&lt;/strong&gt; из одноимённых аниме и манги. Обложка украшена узнаваемой белой надписью &amp;laquo;Death Note&amp;raquo;, повторяющей дизайн тетради Лайта Ягами.&lt;/p&gt;
-&lt;p&gt;Отличный вариант для &lt;strong data-end="1122" data-start="1037"&gt;фанатов Death Note, коллекционеров аниме-мерча, косплея или тематического подарка&lt;/strong&gt;. Можно использовать как обычный блокнот для записей, заметок и идей.&lt;/p&gt;</t>
+          <t>&lt;p data-end="1033" data-start="837"&gt;Чёрные полупрозрачные капроновые колготки с крупным готическим принтом в виде пауков и паутины. Контрастный узор проходит вдоль ног и делает колготки выразительным акцентом образа.&lt;/p&gt;
+&lt;p data-end="1153" data-start="1035"&gt;Отлично подойдут для &lt;strong data-end="1152" data-start="1056"&gt;готических и альтернативных образов, Halloween, косплея, тематических вечеринок и фотосессий&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;p data-end="266" data-start="64"&gt;Чорний зошит, виконаний у стилі легендарного &lt;strong data-end="135" data-start="121"&gt;Death Note&lt;/strong&gt; з однойменного аніме та манґи. Обкладинка оформлена впізнаваним білим написом &amp;laquo;Death Note&amp;raquo;, що повторює дизайн зошита Лайта Яґамі.&lt;/p&gt;
-&lt;p data-end="446" data-start="268"&gt;Чудовий варіант для &lt;strong data-end="372" data-start="288"&gt;фанатів Death Note, колекціонерів аніме-мерчу, косплею або тематичного подарунка&lt;/strong&gt;. Можна використовувати як звичайний блокнот для записів, нотаток та ідей.&lt;/p&gt;</t>
+          <t>&lt;p data-end="272" data-start="76"&gt;Чорні напівпрозорі капронові колготки з великим готичним принтом у вигляді павуків та павутиння. Контрастний візерунок проходить уздовж ніг та робить колготки виразним акцентом образу.&lt;/p&gt;
+&lt;p data-end="386" data-start="274"&gt;Чудово підійдуть для &lt;strong data-end="385" data-start="295"&gt;готичних та альтернативних образів, Halloween, косплею, тематичних вечірок і фотосесій&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1785,7 +1721,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1802,7 +1738,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7659947329_tetrad-death-note.jpg</t>
+          <t>https://images.prom.ua/7659939209_kapronovye-kolgotki-s.jpg</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1814,24 +1750,24 @@
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://prom.ua/Tetradi-uchenicheskie</t>
+          <t>https://prom.ua/Kolgoty-i-chulki-zhenskie</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>3171908831</v>
+        <v>3171906742</v>
       </c>
       <c r="AA9" t="n">
-        <v>211118</v>
+        <v>304</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1840,7 +1776,7 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3171908831-tetrad-death-note.html</t>
+          <t>https://cs4101246.prom.ua/p3171906742-kapronovye-kolgotki-paukami.html</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr"/>
@@ -1865,43 +1801,76 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>Колір</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Чорний</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Вид виробу</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>Колготки</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Капронові</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0552768211839</t>
+          <t>7986450951302</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Мягкая игрушка Лук 42 см</t>
+          <t>Китайская шляпа с красной вуалью</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>М’яка іграшка Цибуля 42 см</t>
+          <t>Китайський капелюх з червоною вуаллю</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>мягкая игрушка лук, плюшевый лук, зелёный лук игрушка, игрушка овощ, плюшевый овощ, забавная игрушка, необычная мягкая игрушка, игрушка 42 см, плюшевая еда, лук плюш, green onion plush, scallion plush, vegetable plush, food plush, funny plush toy</t>
+          <t>китайская шляпа, шляпа с вуалью, красная шляпа, чёрная шляпа, шляпа для косплея, китайский головной убор, восточная шляпа, шляпа с лентами, шляпа с кисточками, азиатский стиль, китайский косплей, Chinese hat, cosplay hat, Chinese cosplay, red veil hat, traditional Chinese hat, oriental hat, hanfu accessories</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>м’яка іграшка цибуля, плюшева цибуля, зелена цибуля іграшка, іграшка овоч, плюшевий овоч, кумедна іграшка, незвичайна м’яка іграшка, іграшка 42 см, плюшева їжа, цибуля плюш, green onion plush, scallion plush, vegetable plush, food plush, funny plush toy</t>
+          <t>китайський капелюх, капелюх з вуаллю, червоний капелюх, чорний капелюх, капелюх для косплею, китайський головний убір, східний капелюх, капелюх зі стрічками, капелюх з китицями, азійський стиль, китайський косплей, Chinese hat, cosplay hat, Chinese cosplay, red veil hat, traditional Chinese hat, oriental hat, hanfu accessories</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Забавная мягкая игрушка в виде зелёного лука. Имеет вытянутую форму и яркие зелёные листья. Благодаря необычному дизайну станет весёлым подарком, дополнением коллекции или оригинальным декором комнаты.&lt;/p&gt;
-&lt;p&gt;Размер: &lt;strong data-end="908" data-start="899"&gt;42 см&lt;/strong&gt;.&lt;/p&gt;</t>
+          <t>&lt;p data-end="1186" data-start="914"&gt;Эффектная декоративная шляпа в традиционном китайском стиле, выполненная в чёрно-красных цветах. Широкие плетёные поля украшены подвесками, кисточками и декоративными элементами, а длинные полупрозрачные красные и чёрные ленты создают выразительный силуэт.&lt;/p&gt;
+&lt;p data-end="1309" data-start="1188"&gt;Отлично подойдёт для &lt;strong data-end="1308" data-start="1209"&gt;косплея, фотосессий, сценических выступлений, образов в восточном стиле и тематических костюмов&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;p data-end="273" data-start="59"&gt;Кумедна м&amp;rsquo;яка іграшка у вигляді зеленої цибулі. Має видовжену форму та яскраве зелене листя. Завдяки незвичайному дизайну стане веселим подарунком, доповненням колекції або оригінальним декором кімнати.&lt;/p&gt;
-&lt;p data-end="293" data-start="275"&gt;Розмір: &lt;strong data-end="292" data-start="283"&gt;42 см&lt;/strong&gt;.&lt;/p&gt;</t>
+          <t>&lt;p data-end="334" data-start="69"&gt;Ефектний декоративний капелюх у традиційному китайському стилі, виконаний у чорно-червоних кольорах. Широкі плетені поля прикрашені підвісками, китицями та декоративними елементами, а довгі напівпрозорі червоні й чорні стрічки створюють виразний силует.&lt;/p&gt;
+&lt;p data-end="447" data-start="336"&gt;Чудово підійде для &lt;strong data-end="446" data-start="355"&gt;косплею, фотосесій, сценічних виступів, образів у східному стилі та тематичних костюмів&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1911,7 +1880,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1928,7 +1897,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7659976167_myagkaya-igrushka-luk.jpg</t>
+          <t>https://images.prom.ua/7659967717_kitajskaya-shlyapa-s.jpg</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1940,24 +1909,24 @@
         <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>152656503</v>
+        <v>152656497</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Мерч</t>
+          <t>Аксесуари</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://prom.ua/Myagkie-plyushevye-igrushki</t>
+          <t>https://prom.ua/Formennye-golovnye-ubory</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="n">
-        <v>3171910700</v>
+        <v>3171909978</v>
       </c>
       <c r="AA10" t="n">
-        <v>2604</v>
+        <v>32714</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1966,7 +1935,7 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>https://cs4101246.prom.ua/p3171910700-myagkaya-igrushka-luk.html</t>
+          <t>https://cs4101246.prom.ua/p3171909978-kitajskaya-shlyapa-krasnoj.html</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr"/>
@@ -1999,419 +1968,7 @@
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>Зелений</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4502081265913</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Мягкая игрушка Мику Хацунэ 35 см — Hatsune Miku</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>М’яка іграшка Міку Хатсуне 35 см — Hatsune Miku</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>мягкая игрушка Мику, Мику Хацунэ, Хацунэ Мику, игрушка Hatsune Miku, плюшевая Мику, плюш Hatsune Miku, Vocaloid, Вокалоид, Мику Vocaloid, аниме игрушка, японская мягкая игрушка, плюшевая игрушка 35 см, Hatsune Miku plush, Miku plush, Vocaloid plush, Hatsune Miku toy, Miku toy</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>м’яка іграшка Міку, Міку Хатсуне, Хацуне Міку, іграшка Hatsune Miku, плюшева Міку, плюш Hatsune Miku, Vocaloid, Вокалоїд, Міку Vocaloid, аніме іграшка, японська м’яка іграшка, плюшева іграшка 35 см, Hatsune Miku plush, Miku plush, Vocaloid plush, Hatsune Miku toy, Miku toy</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>&lt;p data-end="1084" data-start="891"&gt;Мягкая игрушка в виде &lt;strong data-end="944" data-start="929"&gt;Хацунэ Мику&lt;/strong&gt; &amp;mdash; виртуальной певицы Vocaloid. Игрушка выполнена в узнаваемом образе Мику: бирюзовые длинные хвостики, наушники, галстук и фирменный наряд.&lt;/p&gt;
-&lt;p data-end="1269" data-start="1086"&gt;Милый дизайн делает её отличным подарком для поклонников Hatsune Miku, Vocaloid и японской поп-культуры. Подойдёт для коллекции, декора комнаты или в качестве уютной плюшевой игрушки.&lt;/p&gt;
-&lt;p data-end="1289" data-start="1271"&gt;Размер: &lt;strong data-end="1288" data-start="1279"&gt;35 см&lt;/strong&gt;.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>&lt;p data-end="274" data-start="80"&gt;М&amp;rsquo;яка іграшка у вигляді &lt;strong data-end="131" data-start="116"&gt;Хацуне Міку&lt;/strong&gt; &amp;mdash; віртуальної співачки Vocaloid. Іграшка виконана у впізнаваному образі Міку: бірюзові довгі хвостики, навушники, краватка та фірмове вбрання.&lt;/p&gt;
-&lt;p data-end="453" data-start="276"&gt;Милий дизайн робить її чудовим подарунком для шанувальників Hatsune Miku, Vocaloid та японської попкультури. Підійде для колекції, декору кімнати або як затишна плюшева іграшка.&lt;/p&gt;
-&lt;p data-end="473" data-start="455"&gt;Розмір: &lt;strong data-end="472" data-start="463"&gt;35 см&lt;/strong&gt;.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>UAH</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>https://images.prom.ua/7660012239_myagkaya-igrushka-miku.jpg</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>152656503</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Мерч</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>https://prom.ua/Myagkie-plyushevye-igrushki</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="n">
-        <v>3171916372</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2604</v>
-      </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>https://cs4101246.prom.ua/p3171916372-myagkaya-igrushka-miku.html</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Одеса</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Так</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>Колір</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>Бірюзовий</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2410085874637</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Мягкая игрушка разноцветный кот 45 см</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>М’яка іграшка різнокольоровий кіт 45 см</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>мягкая игрушка кот, плюшевый кот, разноцветный кот, трёхцветный кот, игрушка котик, плюшевый котик, кот 45 см, мягкая игрушка 45 см, подушка кот, игрушка подушка, длинный кот, милый котик, kawaii кот, kawaii cat, plush cat, cat plush, calico cat plush, cat pillow, stuffed cat</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>м’яка іграшка кіт, плюшевий кіт, різнокольоровий кіт, триколірний кіт, іграшка котик, плюшевий котик, кіт 45 см, м’яка іграшка 45 см, подушка кіт, іграшка подушка, довгий кіт, милий котик, kawaii кіт, kawaii cat, plush cat, cat plush, calico cat plush, cat pillow, stuffed cat</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>&lt;p data-end="1042" data-start="861"&gt;Милая мягкая игрушка в виде пухленького трёхцветного котика. Сочетание белого, рыжего и чёрного цветов и забавное выражение мордочки придают игрушке особый характер.&lt;/p&gt;
-&lt;p data-end="1232" data-start="1044"&gt;Благодаря вытянутой форме котика можно использовать не только как игрушку, но и как декоративную подушку для кровати или дивана. Отличный вариант подарка для любителей котов и милых вещей.&lt;/p&gt;
-&lt;p data-end="1252" data-start="1234"&gt;Размер: &lt;strong data-end="1251" data-start="1242"&gt;45 см&lt;/strong&gt;.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>&lt;p data-end="254" data-start="72"&gt;Мила м&amp;rsquo;яка іграшка у вигляді пухкенького триколірного котика. Поєднання білого, рудого та чорного кольорів і кумедний вираз мордочки надають іграшці особливого характеру.&lt;/p&gt;
-&lt;p data-end="440" data-start="256"&gt;Завдяки витягнутій формі котика можна використовувати не лише як іграшку, а й як декоративну подушку для ліжка або дивана. Чудовий варіант для подарунка любителям котів та милих речей.&lt;/p&gt;
-&lt;p data-end="460" data-start="442"&gt;Розмір: &lt;strong data-end="459" data-start="450"&gt;45 см&lt;/strong&gt;.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>UAH</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>https://images.prom.ua/7668984067_myagkaya-igrushka-raznotsvetnyj.jpg, https://images.prom.ua/7668984069_myagkaya-igrushka-raznotsvetnyj.jpg</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>152656503</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Мерч</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>https://prom.ua/Myagkie-plyushevye-igrushki</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="n">
-        <v>3175848650</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2604</v>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>https://cs4101246.prom.ua/p3175848650-myagkaya-igrushka-raznotsvetnyj.html</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Одеса</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Так</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2886545079061</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Печенье Oreo × BTS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Печиво Oreo × BTS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Oreo BTS, печенье BTS, Орео BTS, Oreo x BTS, BTS Oreo, BTS печенье, печенье K-pop, BTS мерч, БТС мерч, корейские сладости, корейское печенье, Oreo Hotteok, BTS Hotteok, K-pop сладости, подарок BTS, Bangtan Boys, ARMY BTS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Oreo BTS, печиво BTS, Орео BTS, Oreo x BTS, BTS Oreo, BTS печиво, печиво K-pop, BTS мерч, БТС мерч, корейські солодощі, корейське печиво, Oreo Hotteok, BTS Hotteok, K-pop солодощі, BTS подарунок, Bangtan Boys, ARMY BTS</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>&lt;p data-end="915" data-start="738"&gt;Лимитированное печенье Oreo в коллаборации с BTS. Оригинальная тематическая упаковка выполнена в фирменном стиле BTS, а само печенье имеет яркий фиолетовый цвет.&lt;/p&gt;
-&lt;p data-end="1030" data-start="917"&gt;Отличный вариант для поклонников BTS, коллекционеров K-pop мерча или в качестве необычного тематического подарка.&lt;/p&gt;
-&lt;p data-end="1152" data-start="1032"&gt;&lt;strong data-end="1040" data-start="1032"&gt;Вес:&lt;/strong&gt; 100 г&lt;br data-end="1049" data-start="1046"/&gt;
-&lt;strong data-end="1058" data-start="1049"&gt;Вкус:&lt;/strong&gt; Hotteok (корейские сладкие блинчики)&lt;br data-end="1098" data-start="1095"/&gt;
-&lt;strong data-end="1115" data-start="1098"&gt;Коллаборация:&lt;/strong&gt; Oreo &amp;times; BTS&lt;br data-end="1129" data-start="1126"/&gt;
-&lt;strong data-end="1140" data-start="1129"&gt;Фандом:&lt;/strong&gt; BTS / K-pop&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>&lt;p data-end="214" data-start="50"&gt;Лімітоване печиво Oreo у колаборації з BTS. Оригінальна тематична упаковка оформлена у фірмовому стилі BTS, а саме печиво має яскравий фіолетовий колір.&lt;/p&gt;
-&lt;p data-end="321" data-start="216"&gt;Чудовий варіант для шанувальників BTS, колекціонерів K-pop мерчу або як незвичайний тематичний подарунок.&lt;/p&gt;
-&lt;p data-end="441" data-start="323"&gt;&lt;strong data-end="332" data-start="323"&gt;Вага:&lt;/strong&gt; 100 г&lt;br data-end="341" data-start="338"/&gt;
-&lt;strong data-end="350" data-start="341"&gt;Смак:&lt;/strong&gt; Hotteok (корейські солодкі млинці)&lt;br data-end="388" data-start="385"/&gt;
-&lt;strong data-end="404" data-start="388"&gt;Колаборація:&lt;/strong&gt; Oreo &amp;times; BTS&lt;br data-end="418" data-start="415"/&gt;
-&lt;strong data-end="429" data-start="418"&gt;Фандом:&lt;/strong&gt; BTS / K-pop&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>UAH</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>https://images.prom.ua/7669011157_pechene-oreo-.jpg</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>152656503</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Мерч</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>https://prom.ua/Pechene-pryaniki</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>3175863978</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2181703</v>
-      </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>https://cs4101246.prom.ua/p3175863978-pechene-oreo-bts.html</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Одеса</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Так</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>Вид виробу</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>Печиво</t>
+          <t>Червоний</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2172,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7518383133_pariki.jpg</t>
+          <t>https://images.prom.ua/7477865666_pariki.jpg</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2210,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7502800702_kosplej.jpg</t>
+          <t>https://images.prom.ua/7518383614_kosplej.jpg</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2248,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7471020559_lolita-fashion.jpg</t>
+          <t>https://images.prom.ua/7253826071_lolita-fashion.jpg</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2316,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7512538938_aksesuari.jpg</t>
+          <t>https://images.prom.ua/7659939209_aksesuari.jpg</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2424,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://images.prom.ua/7502814610_merch.jpg</t>
+          <t>https://images.prom.ua/7669011157_merch.jpg</t>
         </is>
       </c>
     </row>
